--- a/results/02_taxa_assemblage/WardsClustering/tables/site_robustness.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/tables/site_robustness.xlsx
@@ -477,22 +477,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.815054349444824</v>
+        <v>0.847936693689849</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6378</v>
+        <v>0.2905</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9312</v>
+        <v>0.6855</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1582</v>
+        <v>0.4176</v>
       </c>
       <c r="G2" t="n">
-        <v>0.773</v>
+        <v>0.2679</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -510,19 +510,19 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>0.752041676123376</v>
+        <v>0.886603392782555</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4361</v>
+        <v>0.4228</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9961</v>
+        <v>0.9911</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0089</v>
+        <v>0.1067</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9871</v>
+        <v>0.8844</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -537,26 +537,26 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>0.815054349444824</v>
+        <v>0.847936693689849</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4139</v>
+        <v>0.2019</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8715000000000001</v>
+        <v>0.6468</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2722</v>
+        <v>0.46</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5993000000000001</v>
+        <v>0.1868</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
     </row>
@@ -570,19 +570,19 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>0.911393090850774</v>
+        <v>0.847936693689849</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1066</v>
+        <v>0.2365</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7187</v>
+        <v>0.6641</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3932</v>
+        <v>0.4453</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3255</v>
+        <v>0.2187</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -600,23 +600,23 @@
         <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>0.752041676123376</v>
+        <v>0.886603392782555</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7141999999999999</v>
+        <v>0.2387</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9968</v>
+        <v>0.9478</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0083</v>
+        <v>0.1701</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9885</v>
+        <v>0.7776</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
     </row>
@@ -630,19 +630,19 @@
         <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>0.752041676123376</v>
+        <v>0.886603392782555</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7302</v>
+        <v>0.5305</v>
       </c>
       <c r="E7" t="n">
-        <v>0.996</v>
+        <v>0.9913999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0086</v>
+        <v>0.1154</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9875</v>
+        <v>0.8761</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -657,22 +657,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>0.815054349444824</v>
+        <v>0.847936693689849</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3897</v>
+        <v>0.236</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6155</v>
+        <v>0.8149</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4623</v>
+        <v>0.0931</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1533</v>
+        <v>0.7217</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -690,19 +690,19 @@
         <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>0.752041676123376</v>
+        <v>0.886603392782555</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7214</v>
+        <v>0.364</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9961</v>
+        <v>0.9959</v>
       </c>
       <c r="F9" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.1074</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9871</v>
+        <v>0.8885</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -717,22 +717,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>0.815054349444824</v>
+        <v>0.847936693689849</v>
       </c>
       <c r="D10" t="n">
-        <v>0.632</v>
+        <v>0.3921</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9292</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1672</v>
+        <v>0.0833</v>
       </c>
       <c r="G10" t="n">
-        <v>0.762</v>
+        <v>0.7247</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -750,19 +750,19 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>0.752041676123376</v>
+        <v>0.886603392782555</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7164</v>
+        <v>0.5393</v>
       </c>
       <c r="E11" t="n">
-        <v>0.996</v>
+        <v>0.9919</v>
       </c>
       <c r="F11" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.1084</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9872</v>
+        <v>0.8835</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -780,19 +780,19 @@
         <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>0.752041676123376</v>
+        <v>0.886603392782555</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7158</v>
+        <v>0.4932</v>
       </c>
       <c r="E12" t="n">
-        <v>0.996</v>
+        <v>0.9944</v>
       </c>
       <c r="F12" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.1023</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9875</v>
+        <v>0.8921</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -807,26 +807,26 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>0.815054349444824</v>
+        <v>0.847936693689849</v>
       </c>
       <c r="D13" t="n">
-        <v>0.443</v>
+        <v>0.1748</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9301</v>
+        <v>0.6813</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1787</v>
+        <v>0.4036</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7514</v>
+        <v>0.2777</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
     </row>
@@ -837,26 +837,26 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>0.815054349444824</v>
+        <v>0.847936693689849</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5634</v>
+        <v>0.1595</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9313</v>
+        <v>0.6412</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1604</v>
+        <v>0.4612</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7709</v>
+        <v>0.1801</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
     </row>
@@ -867,22 +867,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>0.815054349444824</v>
+        <v>0.847936693689849</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6308</v>
+        <v>0.4185</v>
       </c>
       <c r="E15" t="n">
-        <v>0.929</v>
+        <v>0.8062</v>
       </c>
       <c r="F15" t="n">
-        <v>0.178</v>
+        <v>0.0858</v>
       </c>
       <c r="G15" t="n">
-        <v>0.751</v>
+        <v>0.7204</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -900,19 +900,19 @@
         <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>0.752041676123376</v>
+        <v>0.886603392782555</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6937</v>
+        <v>0.3176</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9973</v>
+        <v>0.9837</v>
       </c>
       <c r="F16" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.1336</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9885</v>
+        <v>0.8501</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -930,23 +930,23 @@
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>0.911393090850774</v>
+        <v>0.847936693689849</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3562</v>
+        <v>0.1763</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7958</v>
+        <v>0.7059</v>
       </c>
       <c r="F17" t="n">
-        <v>0.062</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7339</v>
+        <v>0.6262</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
     </row>
@@ -960,19 +960,19 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>0.752041676123376</v>
+        <v>0.886603392782555</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7291</v>
+        <v>0.5745</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9959</v>
+        <v>0.9893</v>
       </c>
       <c r="F18" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.1083</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9869</v>
+        <v>0.881</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -987,22 +987,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>0.911393090850774</v>
+        <v>0.718546723494759</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1243</v>
+        <v>0.1618</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6686</v>
+        <v>0.788</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4409</v>
+        <v>0.3017</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2277</v>
+        <v>0.4863</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1020,23 +1020,23 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>0.911393090850774</v>
+        <v>0.847936693689849</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0595</v>
+        <v>0.1139</v>
       </c>
       <c r="E20" t="n">
-        <v>0.531</v>
+        <v>0.6356000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>0.591</v>
+        <v>0.4782</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.06</v>
+        <v>0.1574</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Uncertain</t>
+          <t>Peripheral</t>
         </is>
       </c>
     </row>
@@ -1050,19 +1050,19 @@
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>0.911393090850774</v>
+        <v>0.847936693689849</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0017</v>
+        <v>0.109</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5629</v>
+        <v>0.62</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.4884</v>
       </c>
       <c r="G21" t="n">
-        <v>0.007</v>
+        <v>0.1316</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1080,19 +1080,19 @@
         <v>2</v>
       </c>
       <c r="C22" t="n">
-        <v>0.752041676123376</v>
+        <v>0.886603392782555</v>
       </c>
       <c r="D22" t="n">
-        <v>0.7355</v>
+        <v>0.5677</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9969</v>
+        <v>0.9898</v>
       </c>
       <c r="F22" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.1115</v>
       </c>
       <c r="G22" t="n">
-        <v>0.9882</v>
+        <v>0.8783</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1107,26 +1107,26 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C23" t="n">
-        <v>0.911393090850774</v>
+        <v>0.718546723494759</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0282</v>
+        <v>0.1883</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6186</v>
+        <v>0.8149</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3206</v>
+        <v>0.2592</v>
       </c>
       <c r="G23" t="n">
-        <v>0.298</v>
+        <v>0.5557</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Uncertain</t>
+          <t>Peripheral</t>
         </is>
       </c>
     </row>
@@ -1140,23 +1140,23 @@
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>0.911393090850774</v>
+        <v>0.847936693689849</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3631</v>
+        <v>0.1949</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8027</v>
+        <v>0.8135</v>
       </c>
       <c r="F24" t="n">
-        <v>0.06370000000000001</v>
+        <v>0.102</v>
       </c>
       <c r="G24" t="n">
-        <v>0.739</v>
+        <v>0.7115</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
     </row>
@@ -1170,23 +1170,23 @@
         <v>3</v>
       </c>
       <c r="C25" t="n">
-        <v>0.815054349444824</v>
+        <v>0.718546723494759</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2605</v>
+        <v>-0.0313</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9318</v>
+        <v>0.6991000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1705</v>
+        <v>0.4119</v>
       </c>
       <c r="G25" t="n">
-        <v>0.7613</v>
+        <v>0.2873</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Uncertain</t>
         </is>
       </c>
     </row>
@@ -1197,26 +1197,26 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>0.815054349444824</v>
+        <v>0.847936693689849</v>
       </c>
       <c r="D26" t="n">
-        <v>0.321</v>
+        <v>0.4032</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4625</v>
+        <v>0.7691</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5679</v>
+        <v>0.2885</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.1054</v>
+        <v>0.4806</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Uncertain</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -1230,23 +1230,23 @@
         <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>0.911393090850774</v>
+        <v>0.847936693689849</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0208</v>
+        <v>0.3694</v>
       </c>
       <c r="E27" t="n">
-        <v>0.8092</v>
+        <v>0.8109</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1452</v>
+        <v>0.0868</v>
       </c>
       <c r="G27" t="n">
-        <v>0.664</v>
+        <v>0.724</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -1260,23 +1260,23 @@
         <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>0.911393090850774</v>
+        <v>0.847936693689849</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.1204</v>
+        <v>0.2394</v>
       </c>
       <c r="E28" t="n">
-        <v>0.8078</v>
+        <v>0.8139</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1528</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>0.655</v>
+        <v>0.7221</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Uncertain</t>
+          <t>Peripheral</t>
         </is>
       </c>
     </row>
@@ -1290,23 +1290,23 @@
         <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>0.911393090850774</v>
+        <v>0.847936693689849</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3477</v>
+        <v>0.1017</v>
       </c>
       <c r="E29" t="n">
-        <v>0.7937</v>
+        <v>0.7438</v>
       </c>
       <c r="F29" t="n">
-        <v>0.063</v>
+        <v>0.1094</v>
       </c>
       <c r="G29" t="n">
-        <v>0.7307</v>
+        <v>0.6343</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
     </row>
@@ -1317,22 +1317,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>0.815054349444824</v>
+        <v>0.847936693689849</v>
       </c>
       <c r="D30" t="n">
-        <v>0.6304999999999999</v>
+        <v>0.4355</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9311</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>0.1791</v>
+        <v>0.0914</v>
       </c>
       <c r="G30" t="n">
-        <v>0.752</v>
+        <v>0.7207</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1350,23 +1350,23 @@
         <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>0.911393090850774</v>
+        <v>0.847936693689849</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1745</v>
+        <v>0.3788</v>
       </c>
       <c r="E31" t="n">
-        <v>0.8177</v>
+        <v>0.8119</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1165</v>
+        <v>0.0955</v>
       </c>
       <c r="G31" t="n">
-        <v>0.7012</v>
+        <v>0.7164</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -1380,23 +1380,23 @@
         <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>0.911393090850774</v>
+        <v>0.847936693689849</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0311</v>
+        <v>0.4303</v>
       </c>
       <c r="E32" t="n">
-        <v>0.8088</v>
+        <v>0.8179</v>
       </c>
       <c r="F32" t="n">
-        <v>0.1389</v>
+        <v>0.0935</v>
       </c>
       <c r="G32" t="n">
-        <v>0.6699000000000001</v>
+        <v>0.7244</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Peripheral</t>
+          <t>Core</t>
         </is>
       </c>
     </row>
@@ -1410,23 +1410,23 @@
         <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>0.911393090850774</v>
+        <v>0.847936693689849</v>
       </c>
       <c r="D33" t="n">
-        <v>0.3345</v>
+        <v>0.2038</v>
       </c>
       <c r="E33" t="n">
-        <v>0.8027</v>
+        <v>0.8119</v>
       </c>
       <c r="F33" t="n">
-        <v>0.062</v>
+        <v>0.0887</v>
       </c>
       <c r="G33" t="n">
-        <v>0.7406</v>
+        <v>0.7233000000000001</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
     </row>
@@ -1437,26 +1437,26 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C34" t="n">
-        <v>0.752041676123376</v>
+        <v>0.718546723494759</v>
       </c>
       <c r="D34" t="n">
-        <v>0.38</v>
+        <v>0.1559</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9885</v>
+        <v>0.7178</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0209</v>
+        <v>0.2309</v>
       </c>
       <c r="G34" t="n">
-        <v>0.9676</v>
+        <v>0.4869</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
     </row>
@@ -1467,22 +1467,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>0.815054349444824</v>
+        <v>0.847936693689849</v>
       </c>
       <c r="D35" t="n">
-        <v>0.6587</v>
+        <v>0.4175</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9298999999999999</v>
+        <v>0.8115</v>
       </c>
       <c r="F35" t="n">
-        <v>0.1595</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="G35" t="n">
-        <v>0.7705</v>
+        <v>0.7196</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -1497,22 +1497,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>0.815054349444824</v>
+        <v>0.847936693689849</v>
       </c>
       <c r="D36" t="n">
-        <v>0.6732</v>
+        <v>0.3285</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9323</v>
+        <v>0.8147</v>
       </c>
       <c r="F36" t="n">
-        <v>0.1661</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="G36" t="n">
-        <v>0.7662</v>
+        <v>0.7219</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -1527,22 +1527,22 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>0.815054349444824</v>
+        <v>0.847936693689849</v>
       </c>
       <c r="D37" t="n">
-        <v>0.578</v>
+        <v>0.3613</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.8072</v>
       </c>
       <c r="F37" t="n">
-        <v>0.1877</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="G37" t="n">
-        <v>0.7464</v>
+        <v>0.7265</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -1557,22 +1557,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C38" t="n">
-        <v>0.815054349444824</v>
+        <v>0.847936693689849</v>
       </c>
       <c r="D38" t="n">
-        <v>0.6139</v>
+        <v>0.2678</v>
       </c>
       <c r="E38" t="n">
-        <v>0.9306</v>
+        <v>0.7668</v>
       </c>
       <c r="F38" t="n">
-        <v>0.1751</v>
+        <v>0.2667</v>
       </c>
       <c r="G38" t="n">
-        <v>0.7554999999999999</v>
+        <v>0.5001</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -1587,22 +1587,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C39" t="n">
-        <v>0.815054349444824</v>
+        <v>0.847936693689849</v>
       </c>
       <c r="D39" t="n">
-        <v>0.6692</v>
+        <v>0.3143</v>
       </c>
       <c r="E39" t="n">
-        <v>0.9303</v>
+        <v>0.8089</v>
       </c>
       <c r="F39" t="n">
-        <v>0.1655</v>
+        <v>0.1058</v>
       </c>
       <c r="G39" t="n">
-        <v>0.7648</v>
+        <v>0.7030999999999999</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -1620,19 +1620,19 @@
         <v>1</v>
       </c>
       <c r="C40" t="n">
-        <v>0.911393090850774</v>
+        <v>0.847936693689849</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0639</v>
+        <v>0.1037</v>
       </c>
       <c r="E40" t="n">
-        <v>0.7844</v>
+        <v>0.6677999999999999</v>
       </c>
       <c r="F40" t="n">
-        <v>0.1714</v>
+        <v>0.4432</v>
       </c>
       <c r="G40" t="n">
-        <v>0.613</v>
+        <v>0.2246</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -1647,26 +1647,26 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C41" t="n">
-        <v>0.752041676123376</v>
+        <v>0.718546723494759</v>
       </c>
       <c r="D41" t="n">
-        <v>0.4206</v>
+        <v>0.1714</v>
       </c>
       <c r="E41" t="n">
-        <v>0.9892</v>
+        <v>0.7024</v>
       </c>
       <c r="F41" t="n">
-        <v>0.0211</v>
+        <v>0.2664</v>
       </c>
       <c r="G41" t="n">
-        <v>0.9681</v>
+        <v>0.4359</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
     </row>
@@ -1680,19 +1680,19 @@
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>0.911393090850774</v>
+        <v>0.847936693689849</v>
       </c>
       <c r="D42" t="n">
+        <v>0.0935</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.681</v>
+      </c>
+      <c r="F42" t="n">
         <v>0.1042</v>
       </c>
-      <c r="E42" t="n">
-        <v>0.8082</v>
-      </c>
-      <c r="F42" t="n">
-        <v>0.06279999999999999</v>
-      </c>
       <c r="G42" t="n">
-        <v>0.7454</v>
+        <v>0.5768</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -1707,26 +1707,26 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C43" t="n">
-        <v>0.752041676123376</v>
+        <v>0.718546723494759</v>
       </c>
       <c r="D43" t="n">
-        <v>0.3938</v>
+        <v>-0.066</v>
       </c>
       <c r="E43" t="n">
-        <v>0.9959</v>
+        <v>0.5572</v>
       </c>
       <c r="F43" t="n">
-        <v>0.0122</v>
+        <v>0.4249</v>
       </c>
       <c r="G43" t="n">
-        <v>0.9837</v>
+        <v>0.1324</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Uncertain</t>
         </is>
       </c>
     </row>
@@ -1740,19 +1740,19 @@
         <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>0.911393090850774</v>
+        <v>0.847936693689849</v>
       </c>
       <c r="D44" t="n">
-        <v>0.3675</v>
+        <v>0.3467</v>
       </c>
       <c r="E44" t="n">
-        <v>0.8047</v>
+        <v>0.8036</v>
       </c>
       <c r="F44" t="n">
-        <v>0.0645</v>
+        <v>0.0838</v>
       </c>
       <c r="G44" t="n">
-        <v>0.7402</v>
+        <v>0.7198</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -1767,22 +1767,22 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C45" t="n">
-        <v>0.911393090850774</v>
+        <v>0.718546723494759</v>
       </c>
       <c r="D45" t="n">
-        <v>0.1518</v>
+        <v>0.0428</v>
       </c>
       <c r="E45" t="n">
-        <v>0.8345</v>
+        <v>0.7883</v>
       </c>
       <c r="F45" t="n">
-        <v>0.1242</v>
+        <v>0.3196</v>
       </c>
       <c r="G45" t="n">
-        <v>0.7103</v>
+        <v>0.4687</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -1800,23 +1800,23 @@
         <v>3</v>
       </c>
       <c r="C46" t="n">
-        <v>0.815054349444824</v>
+        <v>0.718546723494759</v>
       </c>
       <c r="D46" t="n">
-        <v>0.6159</v>
+        <v>0.0299</v>
       </c>
       <c r="E46" t="n">
-        <v>0.9375</v>
+        <v>0.7723</v>
       </c>
       <c r="F46" t="n">
-        <v>0.1636</v>
+        <v>0.3219</v>
       </c>
       <c r="G46" t="n">
-        <v>0.7739</v>
+        <v>0.4504</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
     </row>
@@ -1827,26 +1827,26 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C47" t="n">
-        <v>0.752041676123376</v>
+        <v>0.718546723494759</v>
       </c>
       <c r="D47" t="n">
-        <v>0.4506</v>
+        <v>0.2219</v>
       </c>
       <c r="E47" t="n">
-        <v>0.9935</v>
+        <v>0.7446</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0158</v>
+        <v>0.2273</v>
       </c>
       <c r="G47" t="n">
-        <v>0.9776</v>
+        <v>0.5173</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Core</t>
+          <t>Peripheral</t>
         </is>
       </c>
     </row>
@@ -1857,26 +1857,26 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C48" t="n">
-        <v>0.911393090850774</v>
+        <v>0.718546723494759</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.2416</v>
+        <v>0.16</v>
       </c>
       <c r="E48" t="n">
-        <v>0.6569</v>
+        <v>0.8227</v>
       </c>
       <c r="F48" t="n">
-        <v>0.4708</v>
+        <v>0.2406</v>
       </c>
       <c r="G48" t="n">
-        <v>0.1862</v>
+        <v>0.5821</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Uncertain</t>
+          <t>Peripheral</t>
         </is>
       </c>
     </row>
@@ -1887,22 +1887,22 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C49" t="n">
-        <v>0.815054349444824</v>
+        <v>0.847936693689849</v>
       </c>
       <c r="D49" t="n">
-        <v>0.6139</v>
+        <v>0.3445</v>
       </c>
       <c r="E49" t="n">
-        <v>0.9325</v>
+        <v>0.7147</v>
       </c>
       <c r="F49" t="n">
-        <v>0.1696</v>
+        <v>0.3874</v>
       </c>
       <c r="G49" t="n">
-        <v>0.7629</v>
+        <v>0.3272</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -1920,19 +1920,19 @@
         <v>1</v>
       </c>
       <c r="C50" t="n">
-        <v>0.911393090850774</v>
+        <v>0.847936693689849</v>
       </c>
       <c r="D50" t="n">
-        <v>0.3411</v>
+        <v>0.3575</v>
       </c>
       <c r="E50" t="n">
-        <v>0.8038</v>
+        <v>0.8052</v>
       </c>
       <c r="F50" t="n">
-        <v>0.0634</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="G50" t="n">
-        <v>0.7403999999999999</v>
+        <v>0.726</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -1947,22 +1947,22 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C51" t="n">
-        <v>0.815054349444824</v>
+        <v>0.847936693689849</v>
       </c>
       <c r="D51" t="n">
-        <v>0.6226</v>
+        <v>0.3168</v>
       </c>
       <c r="E51" t="n">
-        <v>0.9355</v>
+        <v>0.6819</v>
       </c>
       <c r="F51" t="n">
-        <v>0.1674</v>
+        <v>0.4178</v>
       </c>
       <c r="G51" t="n">
-        <v>0.7681</v>
+        <v>0.2641</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
